--- a/data/Nickerie_monthly.xlsx
+++ b/data/Nickerie_monthly.xlsx
@@ -1,21 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\My PC\OneDrive\Documents\Data_Website\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\My PC\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{484E4C05-A665-4409-8A0A-1BB685470619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2B7212-9820-47C8-82F8-9E503642A6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75E4151C-83C8-4044-8DD8-A110A99CA7E5}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{75E4151C-83C8-4044-8DD8-A110A99CA7E5}"/>
   </bookViews>
   <sheets>
     <sheet name="data_products" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data_products!$A$1:$C$792</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -889,8 +905,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8D0163A-8515-4C60-A962-DC06BE00C925}">
-  <dimension ref="A1:C790"/>
+  <dimension ref="A1:C800"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -9499,10 +9518,10 @@
         <v>2025</v>
       </c>
       <c r="B783">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C783">
-        <v>96</v>
+        <v>138.6</v>
       </c>
     </row>
     <row r="784" spans="1:3" x14ac:dyDescent="0.25">
@@ -9510,10 +9529,10 @@
         <v>2025</v>
       </c>
       <c r="B784">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C784">
-        <v>344.8</v>
+        <v>96</v>
       </c>
     </row>
     <row r="785" spans="1:3" x14ac:dyDescent="0.25">
@@ -9521,10 +9540,10 @@
         <v>2025</v>
       </c>
       <c r="B785">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C785">
-        <v>242</v>
+        <v>344.8</v>
       </c>
     </row>
     <row r="786" spans="1:3" x14ac:dyDescent="0.25">
@@ -9532,10 +9551,10 @@
         <v>2025</v>
       </c>
       <c r="B786">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C786">
-        <v>365.8</v>
+        <v>242</v>
       </c>
     </row>
     <row r="787" spans="1:3" x14ac:dyDescent="0.25">
@@ -9543,10 +9562,10 @@
         <v>2025</v>
       </c>
       <c r="B787">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C787">
-        <v>79.7</v>
+        <v>365.8</v>
       </c>
     </row>
     <row r="788" spans="1:3" x14ac:dyDescent="0.25">
@@ -9554,10 +9573,10 @@
         <v>2025</v>
       </c>
       <c r="B788">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C788">
-        <v>8.1</v>
+        <v>191.8</v>
       </c>
     </row>
     <row r="789" spans="1:3" x14ac:dyDescent="0.25">
@@ -9565,10 +9584,10 @@
         <v>2025</v>
       </c>
       <c r="B789">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C789">
-        <v>11.9</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="790" spans="1:3" x14ac:dyDescent="0.25">
@@ -9576,10 +9595,120 @@
         <v>2025</v>
       </c>
       <c r="B790">
+        <v>9</v>
+      </c>
+      <c r="C790">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="791" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A791">
+        <v>2025</v>
+      </c>
+      <c r="B791">
+        <v>10</v>
+      </c>
+      <c r="C791">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="792" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A792">
+        <v>2025</v>
+      </c>
+      <c r="B792">
         <v>11</v>
       </c>
-      <c r="C790">
+      <c r="C792">
         <v>106.9</v>
+      </c>
+    </row>
+    <row r="793" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A793">
+        <v>2025</v>
+      </c>
+      <c r="B793">
+        <v>12</v>
+      </c>
+      <c r="C793">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="794" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A794">
+        <v>2026</v>
+      </c>
+      <c r="B794">
+        <v>1</v>
+      </c>
+      <c r="C794">
+        <v>93.3</v>
+      </c>
+    </row>
+    <row r="795" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A795">
+        <v>2026</v>
+      </c>
+      <c r="B795">
+        <v>2</v>
+      </c>
+      <c r="C795">
+        <v>39.799999999999997</v>
+      </c>
+    </row>
+    <row r="796" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A796">
+        <v>2026</v>
+      </c>
+      <c r="B796">
+        <v>3</v>
+      </c>
+      <c r="C796">
+        <v>364.2</v>
+      </c>
+    </row>
+    <row r="797" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A797">
+        <v>2026</v>
+      </c>
+      <c r="B797">
+        <v>4</v>
+      </c>
+      <c r="C797">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="798" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A798">
+        <v>2026</v>
+      </c>
+      <c r="B798">
+        <v>5</v>
+      </c>
+      <c r="C798">
+        <v>101.2</v>
+      </c>
+    </row>
+    <row r="799" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A799">
+        <v>2026</v>
+      </c>
+      <c r="B799">
+        <v>6</v>
+      </c>
+      <c r="C799">
+        <v>211.9</v>
+      </c>
+    </row>
+    <row r="800" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A800">
+        <v>2026</v>
+      </c>
+      <c r="B800">
+        <v>7</v>
+      </c>
+      <c r="C800">
+        <v>150.69999999999999</v>
       </c>
     </row>
   </sheetData>
